--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1524,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1572,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1591,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1627,788 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -981,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1058,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1102,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1129,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1244,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1355,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1466,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1627,7 +1667,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1688,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1897,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1964,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2075,7 +2123,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2186,7 +2234,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2291,13 +2339,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2305,22 +2357,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2358,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2372,43 +2424,959 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1645,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1661,13 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1705,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1814,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1847,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1958,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,37 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2040,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2073,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2295,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2319,37 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2377,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2410,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,17 +2470,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2454,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2492,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2525,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2549,32 +2589,32 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2640,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2694,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2920,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2981,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3035,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3150,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3255,13 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3371,12 +3415,698 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>82.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>82.5</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2647,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,32 +2708,32 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2762,32 +2766,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -2795,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,33 +2827,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2873,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2906,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,37 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2988,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3021,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,17 +3065,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3065,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3103,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3136,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,17 +3184,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3180,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3305,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3765,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3937,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3991,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3999,22 +4023,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4052,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4066,47 +4090,622 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
         </is>
       </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,14 +3080,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3133,24 +3133,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3242,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3319,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3433,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3472,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3505,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3549,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3587,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3620,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,17 +3656,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3664,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3850,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4245,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4360,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4536,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,22 +4610,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4646,12 +4658,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4665,47 +4677,392 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>11:05</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,18 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3605,24 +3609,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3747,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3779,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3791,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3829,32 +3837,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3862,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,33 +3898,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3940,32 +3956,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3973,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,37 +4017,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4075,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4088,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4136,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4132,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4170,32 +4194,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4203,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4255,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4313,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4318,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,17 +4374,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4362,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4548,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4602,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4893,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4947,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4955,22 +4987,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5003,12 +5035,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5022,47 +5054,737 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>81.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>81.7</t>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>81.7</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4323,24 +4323,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4432,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4493,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4509,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4547,32 +4551,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4580,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4612,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4624,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4662,32 +4670,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4695,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4731,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,12 +4751,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4777,32 +4789,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4810,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4834,37 +4850,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4892,32 +4908,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4925,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,17 +4969,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4969,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5007,32 +5027,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5040,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,17 +5088,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5084,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5122,32 +5146,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5155,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,37 +5207,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5439,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5802,707 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5037,24 +5037,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5156,19 +5156,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5326,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5342,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5380,32 +5384,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,17 +5445,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5457,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5503,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5564,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5572,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5622,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5643,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,32 +5683,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5725,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5758,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5802,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5802,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5955,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5988,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,37 +6036,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6152,12 +6176,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6333,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6502,7 +6526,467 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5751,24 +5751,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5860,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5921,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5937,12 +5941,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5975,36 +5979,32 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6056,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6094,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6155,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6171,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6209,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6242,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6324,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -6357,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6401,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6439,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6472,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,37 +6512,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,7 +7002,467 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,14 +2370,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6461,24 +6461,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6570,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6603,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,12 +6651,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6685,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,37 +6750,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6915,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6948,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,37 +6984,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,7 +7114,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7117,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7145,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7222,12 +7238,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7293,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7408,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7457,12 +7473,817 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,14 +3794,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,14 +5222,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7042,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,17 +7103,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7119,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7167,24 +7171,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7194,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7243,7 +7247,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7276,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7309,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,37 +7341,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7391,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7424,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7468,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7506,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7539,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,32 +7579,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7621,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7654,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7698,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7736,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7769,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7793,37 +7817,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8038,7 +8062,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8114,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8307,927 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
           <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,14 +2727,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,14 +7475,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7528,24 +7528,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7766,24 +7766,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7875,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7908,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,32 +7936,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7990,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8023,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,17 +8055,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8067,12 +8075,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8105,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8138,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,37 +8174,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8220,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8253,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,32 +8293,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8335,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8368,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,37 +8412,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8450,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -8483,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8507,17 +8531,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8527,12 +8551,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8598,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8661,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8713,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8877,7 +8901,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8943,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8997,7 +9021,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9005,22 +9029,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9053,12 +9077,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9107,12 +9131,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9144,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9130,7 +9154,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9168,12 +9192,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9187,47 +9211,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>5/14</t>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,22 +5460,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,17 +5698,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8361,24 +8361,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8589,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8622,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8650,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8666,12 +8670,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8704,32 +8708,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8737,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,32 +8769,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8819,32 +8827,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8852,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8876,32 +8888,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8934,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -8967,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,37 +9007,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9082,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,37 +9126,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9236,7 +9256,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9279,32 +9299,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9312,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,32 +9360,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9427,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9657,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9696,7 +9720,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9711,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9821,12 +9845,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10046,12 +10070,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10117,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10195,812 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
           <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3675,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,22 +5222,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,22 +6765,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,22 +7951,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8670,12 +8670,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9418,32 +9418,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9451,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9479,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9495,17 +9499,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9533,32 +9537,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9566,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9590,37 +9598,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9648,32 +9656,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9681,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,17 +9717,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9725,17 +9737,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9763,32 +9775,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9796,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9820,37 +9836,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9878,32 +9894,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9911,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9935,37 +9955,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9993,32 +10013,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10026,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,17 +10074,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10070,12 +10094,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10108,32 +10132,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10141,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10165,37 +10193,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10310,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10425,7 +10453,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10525,7 +10553,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10601,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10716,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10765,7 +10793,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10831,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10885,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10893,22 +10921,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10941,12 +10969,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10960,47 +10988,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9027,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,17 +9618,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,32 +10251,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10284,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10312,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10328,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10366,32 +10370,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -10399,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,17 +10431,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10443,17 +10451,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10596,32 +10604,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10629,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10653,17 +10665,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10673,12 +10685,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10711,32 +10723,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10744,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10784,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10788,17 +10804,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10826,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10859,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10883,37 +10903,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10941,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10974,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10998,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11018,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11128,7 +11152,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11143,7 +11167,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11319,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11434,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11473,7 +11497,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11549,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11607,6 +11631,351 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8432,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11195,32 +11195,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11228,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11252,17 +11256,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11272,17 +11276,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11310,32 +11314,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11343,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11367,17 +11375,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11387,17 +11395,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11425,32 +11433,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11458,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11482,17 +11494,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11502,17 +11514,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11540,32 +11552,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11573,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11597,17 +11613,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11617,12 +11633,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11655,32 +11671,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11688,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11712,17 +11732,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11732,12 +11752,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11803,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11918,7 +11938,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11962,17 +11982,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-182路.xlsx
+++ b/data/export/2026-10-30-182路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11681,24 +11681,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11790,32 +11790,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11823,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,17 +11851,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11867,12 +11871,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11938,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
